--- a/data/hello_rjesenje.xlsx
+++ b/data/hello_rjesenje.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -3920,6 +3920,414 @@
       </c>
       <c r="R51" t="n">
         <v>72</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16DE3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5591.27</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5220.27</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1407.08</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>12</v>
+      </c>
+      <c r="H52" t="n">
+        <v>9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>85</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>24158</v>
+      </c>
+      <c r="L52" t="n">
+        <v>101</v>
+      </c>
+      <c r="M52" t="n">
+        <v>15</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="P52" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>93.78999999999998</v>
+      </c>
+      <c r="R52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16DE4</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5533.1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5409.15</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>123.9500000000007</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>16</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>79</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>21890</v>
+      </c>
+      <c r="L53" t="n">
+        <v>89</v>
+      </c>
+      <c r="M53" t="n">
+        <v>15</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="P53" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="R53" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16DE5</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5293.52</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>5437.749999999999</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>-144.2299999999996</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-2.65</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>73</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>43038</v>
+      </c>
+      <c r="L54" t="n">
+        <v>66</v>
+      </c>
+      <c r="M54" t="n">
+        <v>15</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="P54" t="n">
+        <v>64.36000000000001</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>83.28</v>
+      </c>
+      <c r="R54" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16DE6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5591.27</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5220.27</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1407.08</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>12</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>85</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>24158</v>
+      </c>
+      <c r="L55" t="n">
+        <v>101</v>
+      </c>
+      <c r="M55" t="n">
+        <v>15</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="P55" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>93.78999999999998</v>
+      </c>
+      <c r="R55" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16DE7</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5407.88</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>5386.139999999999</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>21.74000000000069</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>79</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>21890</v>
+      </c>
+      <c r="L56" t="n">
+        <v>89</v>
+      </c>
+      <c r="M56" t="n">
+        <v>15</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="P56" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>90.11</v>
+      </c>
+      <c r="R56" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16DE8</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>4590.219999999999</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4878.849999999999</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>-288.6300000000001</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-5.92</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>9</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>73</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>43038</v>
+      </c>
+      <c r="L57" t="n">
+        <v>66</v>
+      </c>
+      <c r="M57" t="n">
+        <v>15</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="P57" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>77.19999999999999</v>
+      </c>
+      <c r="R57" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3933,7 +4341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4070,6 +4478,414 @@
       </c>
       <c r="R2" t="n">
         <v>26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16DE3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5409.15</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5591.2699999999995</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>-182.1199999999999</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-3.26</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>25161</v>
+      </c>
+      <c r="L3" t="n">
+        <v>103</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="P3" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>16DE4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5437.749999999999</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5533.1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>-95.35000000000127</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>73</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>11222</v>
+      </c>
+      <c r="L4" t="n">
+        <v>86</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="P4" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>87.41000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16DE5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4698.150000000001</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5293.5199999999995</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-595.369999999999</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-11.25</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>11302</v>
+      </c>
+      <c r="L5" t="n">
+        <v>45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>66.91</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16DE6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5386.139999999999</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5591.2699999999995</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-205.1300000000001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-3.67</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>85</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>25161</v>
+      </c>
+      <c r="L6" t="n">
+        <v>103</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>23.98999999999999</v>
+      </c>
+      <c r="P6" t="n">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="R6" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16DE7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4878.849999999999</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5407.88</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>-529.0300000000007</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-9.78</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>73</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>11222</v>
+      </c>
+      <c r="L7" t="n">
+        <v>86</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="P7" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16DE8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3245.19</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4590.219999999999</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-1345.029999999999</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-29.3</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>47</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>11302</v>
+      </c>
+      <c r="L8" t="n">
+        <v>45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="P8" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4083,7 +4899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4220,6 +5036,414 @@
       </c>
       <c r="R2" t="n">
         <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16DE3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5595.61</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5591.2699999999995</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4.340000000000146</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>20274</v>
+      </c>
+      <c r="L3" t="n">
+        <v>101</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="P3" t="n">
+        <v>69.69</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>93.52999999999999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>16DE4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5407.88</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5533.1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>-125.2200000000003</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>79</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>20482</v>
+      </c>
+      <c r="L4" t="n">
+        <v>89</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="P4" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>90.11</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16DE5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4700.54</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5293.5199999999995</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-592.9799999999996</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-11.2</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>73</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>35834</v>
+      </c>
+      <c r="L5" t="n">
+        <v>66</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="P5" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>78.72999999999999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16DE6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5595.61</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5591.2699999999995</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4.340000000000146</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>85</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>20274</v>
+      </c>
+      <c r="L6" t="n">
+        <v>101</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>69.69</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>93.52999999999999</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16DE7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5407.88</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5407.88</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>79</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>20482</v>
+      </c>
+      <c r="L7" t="n">
+        <v>89</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="P7" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>90.11</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16DE8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4700.54</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4590.219999999999</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>110.3200000000006</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>73</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>35834</v>
+      </c>
+      <c r="L8" t="n">
+        <v>66</v>
+      </c>
+      <c r="M8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="P8" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>78.72999999999999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4233,7 +5457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4372,6 +5596,414 @@
         <v>11</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16DE3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5435.52</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5409.15</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>26.3700000000008</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>23018</v>
+      </c>
+      <c r="L3" t="n">
+        <v>103</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>23.98999999999999</v>
+      </c>
+      <c r="P3" t="n">
+        <v>69.61999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>16DE4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4982.58</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5437.749999999999</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>-455.1699999999992</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>73</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>10711</v>
+      </c>
+      <c r="L4" t="n">
+        <v>86</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16DE5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3280.57</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4698.150000000001</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-1417.58</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-30.17</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10263</v>
+      </c>
+      <c r="L5" t="n">
+        <v>45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>39.59999999999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>52.02000000000001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16DE6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5435.52</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5386.139999999999</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>49.38000000000102</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>85</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>23018</v>
+      </c>
+      <c r="L6" t="n">
+        <v>103</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>23.98999999999999</v>
+      </c>
+      <c r="P6" t="n">
+        <v>69.61999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="R6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16DE7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4982.58</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4878.849999999999</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103.7300000000005</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>73</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>10711</v>
+      </c>
+      <c r="L7" t="n">
+        <v>86</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="P7" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16DE8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3280.57</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3245.19</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>35.38000000000011</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>47</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>10263</v>
+      </c>
+      <c r="L8" t="n">
+        <v>45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="P8" t="n">
+        <v>39.59999999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>52.02000000000001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hello_rjesenje.xlsx
+++ b/data/hello_rjesenje.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4328,6 +4328,414 @@
       </c>
       <c r="R57" t="n">
         <v>39</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16DE9</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3977.23</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3606.23</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>972.03</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>10</v>
+      </c>
+      <c r="H58" t="n">
+        <v>7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>84</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>39343</v>
+      </c>
+      <c r="L58" t="n">
+        <v>104</v>
+      </c>
+      <c r="M58" t="n">
+        <v>15</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P58" t="n">
+        <v>48.98999999999999</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="R58" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16DE10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3788.99</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>-247.0599999999999</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>77</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>43130</v>
+      </c>
+      <c r="L59" t="n">
+        <v>85</v>
+      </c>
+      <c r="M59" t="n">
+        <v>15</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P59" t="n">
+        <v>46.78999999999999</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="R59" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16DE11</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3908.9</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>245.5900000000001</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>74</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>40659</v>
+      </c>
+      <c r="L60" t="n">
+        <v>68</v>
+      </c>
+      <c r="M60" t="n">
+        <v>15</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P60" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="R60" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16DE12</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3977.23</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3606.23</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>972.03</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>10</v>
+      </c>
+      <c r="H61" t="n">
+        <v>7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>84</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>39343</v>
+      </c>
+      <c r="L61" t="n">
+        <v>104</v>
+      </c>
+      <c r="M61" t="n">
+        <v>15</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P61" t="n">
+        <v>48.98999999999999</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="R61" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16DE13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3788.99</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>-247.0599999999999</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>9</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>77</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>43130</v>
+      </c>
+      <c r="L62" t="n">
+        <v>85</v>
+      </c>
+      <c r="M62" t="n">
+        <v>15</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P62" t="n">
+        <v>46.78999999999999</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="R62" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16DE14</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3908.9</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>245.5900000000001</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>9</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>74</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>40659</v>
+      </c>
+      <c r="L63" t="n">
+        <v>68</v>
+      </c>
+      <c r="M63" t="n">
+        <v>15</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P63" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="R63" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -4341,7 +4749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4885,6 +5293,414 @@
         <v>51.98</v>
       </c>
       <c r="R8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16DE9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4036.05</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>58.82000000000016</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>85</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>24888</v>
+      </c>
+      <c r="L9" t="n">
+        <v>110</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="P9" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16DE10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>-125.6799999999998</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>68</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>16042</v>
+      </c>
+      <c r="L10" t="n">
+        <v>79</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>16DE11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3362.99</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>-545.9100000000003</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-13.97</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>47</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>11518</v>
+      </c>
+      <c r="L11" t="n">
+        <v>48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P11" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>16DE12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4036.05</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>58.82000000000016</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>24888</v>
+      </c>
+      <c r="L12" t="n">
+        <v>110</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="P12" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="R12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>16DE13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>-125.6799999999998</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>68</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>16042</v>
+      </c>
+      <c r="L13" t="n">
+        <v>79</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>16DE14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3362.99</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>-545.9100000000003</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-13.97</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>47</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>11518</v>
+      </c>
+      <c r="L14" t="n">
+        <v>48</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P14" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="R14" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4899,7 +5715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5443,6 +6259,414 @@
         <v>78.72999999999999</v>
       </c>
       <c r="R8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16DE9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4116.66</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>139.4300000000003</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>84</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>34833</v>
+      </c>
+      <c r="L9" t="n">
+        <v>104</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P9" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16DE10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3861.82</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>72.82999999999993</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>77</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>36332</v>
+      </c>
+      <c r="L10" t="n">
+        <v>85</v>
+      </c>
+      <c r="M10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P10" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="R10" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>16DE11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3973.7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>64.80000000000018</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>74</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>33002</v>
+      </c>
+      <c r="L11" t="n">
+        <v>68</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="R11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>16DE12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4116.66</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>139.4300000000003</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>34833</v>
+      </c>
+      <c r="L12" t="n">
+        <v>104</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P12" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="R12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>16DE13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3861.82</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>72.82999999999993</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>77</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>36332</v>
+      </c>
+      <c r="L13" t="n">
+        <v>85</v>
+      </c>
+      <c r="M13" t="n">
+        <v>15</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="R13" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>16DE14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3973.7</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>64.80000000000018</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>74</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>33002</v>
+      </c>
+      <c r="L14" t="n">
+        <v>68</v>
+      </c>
+      <c r="M14" t="n">
+        <v>15</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="R14" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5457,7 +6681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -6004,6 +7228,414 @@
         <v>4</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16DE9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4263.77</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>227.7199999999998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>85</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>21317</v>
+      </c>
+      <c r="L9" t="n">
+        <v>110</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16DE10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>68</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>15579</v>
+      </c>
+      <c r="L10" t="n">
+        <v>79</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>16DE11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3374.43</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3362.99</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>11.44000000000005</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>47</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>10744</v>
+      </c>
+      <c r="L11" t="n">
+        <v>48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P11" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>51.83000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>16DE12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4263.77</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>227.7199999999998</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>21317</v>
+      </c>
+      <c r="L12" t="n">
+        <v>110</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="R12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>16DE13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>68</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>15579</v>
+      </c>
+      <c r="L13" t="n">
+        <v>79</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>16DE14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3374.43</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3362.99</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11.44000000000005</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>47</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>10744</v>
+      </c>
+      <c r="L14" t="n">
+        <v>48</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P14" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>51.83000000000001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hello_rjesenje.xlsx
+++ b/data/hello_rjesenje.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4736,6 +4736,482 @@
       </c>
       <c r="R63" t="n">
         <v>48</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16DE15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3977.23</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3606.23</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>972.03</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>10</v>
+      </c>
+      <c r="H64" t="n">
+        <v>7</v>
+      </c>
+      <c r="I64" t="n">
+        <v>84</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>39343</v>
+      </c>
+      <c r="L64" t="n">
+        <v>104</v>
+      </c>
+      <c r="M64" t="n">
+        <v>15</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P64" t="n">
+        <v>48.98999999999999</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="R64" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16DE15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3977.23</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>3606.23</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>972.03</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>10</v>
+      </c>
+      <c r="H65" t="n">
+        <v>7</v>
+      </c>
+      <c r="I65" t="n">
+        <v>84</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>39343</v>
+      </c>
+      <c r="L65" t="n">
+        <v>104</v>
+      </c>
+      <c r="M65" t="n">
+        <v>15</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P65" t="n">
+        <v>48.98999999999999</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="R65" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16DE16</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3788.99</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>-247.0599999999999</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>9</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>77</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>43130</v>
+      </c>
+      <c r="L66" t="n">
+        <v>85</v>
+      </c>
+      <c r="M66" t="n">
+        <v>15</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P66" t="n">
+        <v>46.78999999999999</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="R66" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16DE17</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3908.9</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>245.5900000000001</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>9</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>74</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>40659</v>
+      </c>
+      <c r="L67" t="n">
+        <v>68</v>
+      </c>
+      <c r="M67" t="n">
+        <v>15</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P67" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="R67" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16DE18</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3977.23</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3606.23</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>972.03</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>10</v>
+      </c>
+      <c r="H68" t="n">
+        <v>7</v>
+      </c>
+      <c r="I68" t="n">
+        <v>84</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>39343</v>
+      </c>
+      <c r="L68" t="n">
+        <v>104</v>
+      </c>
+      <c r="M68" t="n">
+        <v>15</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P68" t="n">
+        <v>48.98999999999999</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="R68" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16DE19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3788.99</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>-247.0599999999999</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>9</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>77</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>43130</v>
+      </c>
+      <c r="L69" t="n">
+        <v>85</v>
+      </c>
+      <c r="M69" t="n">
+        <v>15</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P69" t="n">
+        <v>46.78999999999999</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="R69" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16DE20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>3908.9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>245.5900000000001</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>9</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>74</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>40659</v>
+      </c>
+      <c r="L70" t="n">
+        <v>68</v>
+      </c>
+      <c r="M70" t="n">
+        <v>15</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P70" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="R70" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4749,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5702,6 +6178,414 @@
       </c>
       <c r="R14" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>16DE15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4036.05</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>58.82000000000016</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>24888</v>
+      </c>
+      <c r="L15" t="n">
+        <v>110</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="P15" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="R15" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16DE16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>-125.6799999999998</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>68</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>16042</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16DE17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3362.99</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>-545.9100000000003</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-13.97</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>47</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>11518</v>
+      </c>
+      <c r="L17" t="n">
+        <v>48</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P17" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16DE18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4036.05</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>58.82000000000016</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>85</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>24888</v>
+      </c>
+      <c r="L18" t="n">
+        <v>110</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="P18" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16DE19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-125.6799999999998</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>68</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>16042</v>
+      </c>
+      <c r="L19" t="n">
+        <v>79</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16DE20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3362.99</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>-545.9100000000003</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-13.97</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>47</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>11518</v>
+      </c>
+      <c r="L20" t="n">
+        <v>48</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P20" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5715,7 +6599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -6668,6 +7552,414 @@
       </c>
       <c r="R14" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>16DE15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4116.66</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>139.4300000000003</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>84</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>34833</v>
+      </c>
+      <c r="L15" t="n">
+        <v>104</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P15" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16DE16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3861.82</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>72.82999999999993</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>77</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>36332</v>
+      </c>
+      <c r="L16" t="n">
+        <v>85</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P16" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="R16" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16DE17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3973.7</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>64.80000000000018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>74</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>33002</v>
+      </c>
+      <c r="L17" t="n">
+        <v>68</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="R17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16DE18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4116.66</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>139.4300000000003</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>84</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>34833</v>
+      </c>
+      <c r="L18" t="n">
+        <v>104</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P18" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="R18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16DE19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3861.82</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>72.82999999999993</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>77</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>36332</v>
+      </c>
+      <c r="L19" t="n">
+        <v>85</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="R19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16DE20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3973.7</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>64.80000000000018</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>74</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>33002</v>
+      </c>
+      <c r="L20" t="n">
+        <v>68</v>
+      </c>
+      <c r="M20" t="n">
+        <v>15</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="R20" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -6681,7 +7973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -7636,6 +8928,414 @@
         <v>5</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>16DE15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4263.77</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>227.7199999999998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>21317</v>
+      </c>
+      <c r="L15" t="n">
+        <v>110</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16DE16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>68</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>15579</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16DE17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3374.43</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3362.99</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>11.44000000000005</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>47</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>10744</v>
+      </c>
+      <c r="L17" t="n">
+        <v>48</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P17" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>51.83000000000001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16DE18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4263.77</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>227.7199999999998</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>85</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>21317</v>
+      </c>
+      <c r="L18" t="n">
+        <v>110</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="R18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16DE19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>68</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>15579</v>
+      </c>
+      <c r="L19" t="n">
+        <v>79</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16DE20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3374.43</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3362.99</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>11.44000000000005</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>47</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>10744</v>
+      </c>
+      <c r="L20" t="n">
+        <v>48</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P20" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>51.83000000000001</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hello_rjesenje.xlsx
+++ b/data/hello_rjesenje.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5212,6 +5212,210 @@
       </c>
       <c r="R70" t="n">
         <v>55</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16DE21</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3977.23</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3606.23</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>972.03</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>10</v>
+      </c>
+      <c r="H71" t="n">
+        <v>7</v>
+      </c>
+      <c r="I71" t="n">
+        <v>84</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>39343</v>
+      </c>
+      <c r="L71" t="n">
+        <v>104</v>
+      </c>
+      <c r="M71" t="n">
+        <v>15</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P71" t="n">
+        <v>48.98999999999999</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="R71" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16DE22</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3788.99</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>-247.0599999999999</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>9</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>77</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>43130</v>
+      </c>
+      <c r="L72" t="n">
+        <v>85</v>
+      </c>
+      <c r="M72" t="n">
+        <v>15</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P72" t="n">
+        <v>46.78999999999999</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="R72" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16DE23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>3908.9</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>245.5900000000001</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>9</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>74</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>40659</v>
+      </c>
+      <c r="L73" t="n">
+        <v>68</v>
+      </c>
+      <c r="M73" t="n">
+        <v>15</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P73" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="R73" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5225,7 +5429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -6586,6 +6790,210 @@
       </c>
       <c r="R20" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16DE21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4036.05</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>58.82000000000016</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>85</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>24888</v>
+      </c>
+      <c r="L21" t="n">
+        <v>110</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="P21" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="R21" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16DE22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-125.6799999999998</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>68</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>16042</v>
+      </c>
+      <c r="L22" t="n">
+        <v>79</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P22" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16DE23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3362.99</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-545.9100000000003</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-13.97</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>47</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>11518</v>
+      </c>
+      <c r="L23" t="n">
+        <v>48</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P23" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6599,7 +7007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -7960,6 +8368,210 @@
       </c>
       <c r="R20" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16DE21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4116.66</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>139.4300000000003</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>84</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>34833</v>
+      </c>
+      <c r="L21" t="n">
+        <v>104</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P21" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="R21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16DE22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3861.82</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3788.99</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>72.82999999999993</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>77</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>36332</v>
+      </c>
+      <c r="L22" t="n">
+        <v>85</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P22" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="R22" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16DE23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3973.7</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3908.9</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>64.80000000000018</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>74</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>33002</v>
+      </c>
+      <c r="L23" t="n">
+        <v>68</v>
+      </c>
+      <c r="M23" t="n">
+        <v>15</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="R23" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -7973,7 +8585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -9336,6 +9948,210 @@
         <v>5</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16DE21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4263.77</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4036.0499999999997</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>227.7199999999998</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>85</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>21317</v>
+      </c>
+      <c r="L21" t="n">
+        <v>110</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16DE22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3663.31</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>68</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>15579</v>
+      </c>
+      <c r="L22" t="n">
+        <v>79</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P22" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16DE23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3374.43</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3362.99</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>11.44000000000005</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>47</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>10744</v>
+      </c>
+      <c r="L23" t="n">
+        <v>48</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P23" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>51.83000000000001</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hello_rjesenje.xlsx
+++ b/data/hello_rjesenje.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -5416,6 +5416,210 @@
       </c>
       <c r="R73" t="n">
         <v>56</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16DE24</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VRPB1</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3977.23</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3606.23</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>972.03</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>10</v>
+      </c>
+      <c r="H74" t="n">
+        <v>7</v>
+      </c>
+      <c r="I74" t="n">
+        <v>84</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>39343</v>
+      </c>
+      <c r="L74" t="n">
+        <v>104</v>
+      </c>
+      <c r="M74" t="n">
+        <v>15</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P74" t="n">
+        <v>48.98999999999999</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="R74" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16DE25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>VRPB2</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3972.25</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4094.0699999999997</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>-121.8200000000002</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>14</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>77</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>43130</v>
+      </c>
+      <c r="L75" t="n">
+        <v>85</v>
+      </c>
+      <c r="M75" t="n">
+        <v>15</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P75" t="n">
+        <v>48.84999999999999</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>69.97999999999999</v>
+      </c>
+      <c r="R75" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16DE26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>VRPB3</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>4327.46</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3972.45</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>355.0100000000002</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8.94</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>18</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>74</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>40659</v>
+      </c>
+      <c r="L76" t="n">
+        <v>68</v>
+      </c>
+      <c r="M76" t="n">
+        <v>15</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="P76" t="n">
+        <v>52.32000000000001</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>71.56</v>
+      </c>
+      <c r="R76" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -5429,7 +5633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -6994,6 +7198,210 @@
       </c>
       <c r="R23" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16DE24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VRPB11</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4094.07</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>116.8400000000001</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>85</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>24888</v>
+      </c>
+      <c r="L24" t="n">
+        <v>110</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="P24" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="R24" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16DE25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VRPB22</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3972.45</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3972.2499999999995</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.2000000000002728</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>68</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>16042</v>
+      </c>
+      <c r="L25" t="n">
+        <v>79</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="P25" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>67.19</v>
+      </c>
+      <c r="R25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16DE26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VRPB33</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4332.27</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4327.46</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4.809999999999491</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>47</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>11518</v>
+      </c>
+      <c r="L26" t="n">
+        <v>48</v>
+      </c>
+      <c r="M26" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="P26" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7007,7 +7415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -8572,6 +8980,210 @@
       </c>
       <c r="R23" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16DE24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VRPBsaUI1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4116.66</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3977.2299999999996</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>139.4300000000003</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>84</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>34833</v>
+      </c>
+      <c r="L24" t="n">
+        <v>104</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="P24" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="R24" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16DE25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VRPBsaUI2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3861.82</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3972.2499999999995</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-110.4299999999998</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-2.78</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>77</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>36332</v>
+      </c>
+      <c r="L25" t="n">
+        <v>85</v>
+      </c>
+      <c r="M25" t="n">
+        <v>15</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="P25" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="R25" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16DE26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VRPBsaUI3</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3973.7</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4327.46</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-353.7599999999998</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-8.17</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>74</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>33002</v>
+      </c>
+      <c r="L26" t="n">
+        <v>68</v>
+      </c>
+      <c r="M26" t="n">
+        <v>15</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="R26" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -8585,7 +9197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -10152,6 +10764,210 @@
         <v>6</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16DE24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VRPBsaUI11</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4263.77</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4094.0699999999997</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>169.6999999999998</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>85</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>21317</v>
+      </c>
+      <c r="L24" t="n">
+        <v>110</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="R24" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16DE25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VRPBsaUI22</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3663.31</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3972.45</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-309.1399999999999</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-7.78</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>68</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>15579</v>
+      </c>
+      <c r="L25" t="n">
+        <v>79</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P25" t="n">
+        <v>45.20999999999999</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16DE26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VRPBsaUI33</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3374.43</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4332.2699999999995</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-957.8399999999997</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-22.11</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I26" t="n">
+        <v>47</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>10744</v>
+      </c>
+      <c r="L26" t="n">
+        <v>48</v>
+      </c>
+      <c r="M26" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="P26" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>51.83000000000001</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
